--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-06-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-06-2025.xlsx
@@ -859,7 +859,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Error: list index out of range</t>
+          <t>£17.48</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
